--- a/2026_09_28/TA_Cancel_Order_Daily_Report/TA_Cancel_Order_Daily_Report-2026-09-30.xlsx
+++ b/2026_09_28/TA_Cancel_Order_Daily_Report/TA_Cancel_Order_Daily_Report-2026-09-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,80 +521,80 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>477994</v>
+        <v>568962</v>
       </c>
       <c r="B4" t="n">
-        <v>10841</v>
+        <v>21484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>歇腳亭</t>
+          <t>意樂餐廳</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>568962</v>
+        <v>595169</v>
       </c>
       <c r="B5" t="n">
-        <v>21484</v>
+        <v>21503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>意樂餐廳</t>
+          <t>The Brew Corner</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>2/0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>595169</v>
+        <v>615157</v>
       </c>
       <c r="B6" t="n">
-        <v>21503</v>
+        <v>17179</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The Brew Corner</t>
+          <t>歇腳亭</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -609,91 +609,91 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>1/32</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>615157</v>
+        <v>679503</v>
       </c>
       <c r="B7" t="n">
-        <v>17179</v>
+        <v>25020</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>歇腳亭</t>
+          <t>手作功夫茶</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/32</t>
+          <t>2/132</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>679503</v>
+        <v>704657</v>
       </c>
       <c r="B8" t="n">
-        <v>25020</v>
+        <v>27470</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>手作功夫茶</t>
+          <t>意樂餐廳</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0/9</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/132</t>
+          <t>1/63</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>704657</v>
+        <v>710555</v>
       </c>
       <c r="B9" t="n">
-        <v>27470</v>
+        <v>28012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>意樂餐廳</t>
+          <t>Flames</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -703,96 +703,96 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/63</t>
+          <t>1/1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>710555</v>
+        <v>714815</v>
       </c>
       <c r="B10" t="n">
-        <v>28012</v>
+        <v>28175</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Flames</t>
+          <t>CHICKEN FACTORY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>8/85</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>714815</v>
+        <v>715953</v>
       </c>
       <c r="B11" t="n">
-        <v>28175</v>
+        <v>30498</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHICKEN FACTORY</t>
+          <t>燒肉LIKE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8/85</t>
+          <t>2/8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>715953</v>
+        <v>728824</v>
       </c>
       <c r="B12" t="n">
-        <v>30498</v>
+        <v>30595</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>燒肉LIKE</t>
+          <t>八月甜品屋</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -818,19 +818,19 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>728824</v>
+        <v>746234</v>
       </c>
       <c r="B13" t="n">
-        <v>30595</v>
+        <v>30841</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>八月甜品屋</t>
+          <t>養心亭</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -840,25 +840,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>4/37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>746234</v>
+        <v>769517</v>
       </c>
       <c r="B14" t="n">
-        <v>30841</v>
+        <v>32700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>養心亭</t>
+          <t>手作功夫茶</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -868,40 +868,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/37</t>
+          <t>4/73</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>758589</v>
+        <v>790085</v>
       </c>
       <c r="B15" t="n">
-        <v>49735</v>
+        <v>51618</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Misugu Bento</t>
+          <t>印度野</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1/74</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0/80</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -911,63 +911,63 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7/1366</t>
+          <t>1/70</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>769517</v>
+        <v>800877</v>
       </c>
       <c r="B16" t="n">
-        <v>32700</v>
+        <v>57932</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>手作功夫茶</t>
+          <t>Pin To Thai</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2/0</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/73</t>
+          <t>5/72</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>790085</v>
+        <v>822915</v>
       </c>
       <c r="B17" t="n">
-        <v>51618</v>
+        <v>96440</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>印度野</t>
+          <t>手作功夫茶</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -977,25 +977,25 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1/70</t>
+          <t>5/4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>800877</v>
+        <v>823372</v>
       </c>
       <c r="B18" t="n">
-        <v>57932</v>
+        <v>62097</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pin To Thai</t>
+          <t>囍囍 川菜烤魚燒烤</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1005,25 +1005,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6/72</t>
+          <t>1/4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>822915</v>
+        <v>838681</v>
       </c>
       <c r="B19" t="n">
-        <v>96440</v>
+        <v>144316</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>手作功夫茶</t>
+          <t>武士漢堡</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1043,25 +1043,25 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5/4</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>823372</v>
+        <v>848140</v>
       </c>
       <c r="B20" t="n">
-        <v>62097</v>
+        <v>98394</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>囍囍 川菜烤魚燒烤</t>
+          <t>壹檸壹鮮果茶</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1076,25 +1076,25 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>834687</v>
+        <v>865198</v>
       </c>
       <c r="B21" t="n">
-        <v>151616</v>
+        <v>111650</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>大阪章三哥</t>
+          <t>茶痴</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1109,30 +1109,30 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1/54</t>
+          <t>3/48</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>838681</v>
+        <v>869231</v>
       </c>
       <c r="B22" t="n">
-        <v>144316</v>
+        <v>113645</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>武士漢堡</t>
+          <t>茶記研究所</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1142,20 +1142,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>848140</v>
+        <v>872474</v>
       </c>
       <c r="B23" t="n">
-        <v>98394</v>
+        <v>106946</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>壹檸壹鮮果茶</t>
+          <t>臻.茶</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1175,25 +1175,25 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>865198</v>
+        <v>875546</v>
       </c>
       <c r="B24" t="n">
-        <v>111650</v>
+        <v>110406</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>茶痴</t>
+          <t>花都餐廳</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1203,35 +1203,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3/48</t>
+          <t>1/45</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>869231</v>
+        <v>889922</v>
       </c>
       <c r="B25" t="n">
-        <v>113645</v>
+        <v>119801</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>茶記研究所</t>
+          <t>花月冰室</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1241,30 +1241,30 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>872474</v>
+        <v>892782</v>
       </c>
       <c r="B26" t="n">
-        <v>106946</v>
+        <v>121574</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>臻.茶</t>
+          <t>皓廚</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>875546</v>
+        <v>993159</v>
       </c>
       <c r="B27" t="n">
-        <v>110406</v>
+        <v>132329</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>花都餐廳</t>
+          <t>楚苑花甲粉</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1297,30 +1297,30 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1/45</t>
+          <t>7/2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>889922</v>
+        <v>998543</v>
       </c>
       <c r="B28" t="n">
-        <v>119801</v>
+        <v>135078</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>花月冰室</t>
+          <t>Thai Shack</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1340,30 +1340,30 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>892782</v>
+        <v>1004210</v>
       </c>
       <c r="B29" t="n">
-        <v>121574</v>
+        <v>140982</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>皓廚</t>
+          <t>茶大椰</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1373,20 +1373,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>993159</v>
+        <v>1004238</v>
       </c>
       <c r="B30" t="n">
-        <v>132329</v>
+        <v>139985</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>楚苑花甲粉</t>
+          <t>幸運茶點點心</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1406,20 +1406,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7/2</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>998543</v>
+        <v>1013237</v>
       </c>
       <c r="B31" t="n">
-        <v>135078</v>
+        <v>139986</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thai Shack</t>
+          <t>珍品港</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1439,20 +1439,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>1/0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1004210</v>
+        <v>1026590</v>
       </c>
       <c r="B32" t="n">
-        <v>140982</v>
+        <v>146918</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>茶大椰</t>
+          <t>Walk We Eat</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1472,20 +1472,20 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>1/3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1004238</v>
+        <v>1100050</v>
       </c>
       <c r="B33" t="n">
-        <v>139985</v>
+        <v>147423</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>幸運茶點點心</t>
+          <t>串燒王</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1505,20 +1505,20 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1013237</v>
+        <v>1118607</v>
       </c>
       <c r="B34" t="n">
-        <v>139986</v>
+        <v>164029</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>珍品港</t>
+          <t>千昇麵家</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1538,30 +1538,30 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>2/6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1026590</v>
+        <v>1120223</v>
       </c>
       <c r="B35" t="n">
-        <v>146918</v>
+        <v>153340</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Walk We Eat</t>
+          <t>冒喜</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1571,30 +1571,30 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1100050</v>
+        <v>1122631</v>
       </c>
       <c r="B36" t="n">
-        <v>147423</v>
+        <v>156240</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>串燒王</t>
+          <t>卿記工房</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>1/13</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/14</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1604,20 +1604,20 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/245</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1118607</v>
+        <v>1124067</v>
       </c>
       <c r="B37" t="n">
-        <v>164029</v>
+        <v>168281</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>千昇麵家</t>
+          <t>Cupping Room</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1637,86 +1637,86 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1120223</v>
+        <v>1129632</v>
       </c>
       <c r="B38" t="n">
-        <v>153340</v>
+        <v>159413</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>冒喜</t>
+          <t>豐盛燒味</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1122631</v>
+        <v>1139328</v>
       </c>
       <c r="B39" t="n">
-        <v>156240</v>
+        <v>163860</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>卿記工房</t>
+          <t>鰹烏冬</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0/14</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1/245</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1124067</v>
+        <v>1139855</v>
       </c>
       <c r="B40" t="n">
-        <v>168281</v>
+        <v>165669</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cupping Room</t>
+          <t>大勝豬扒·清湯腩</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1731,25 +1731,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1/0</t>
+          <t>5/5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1129632</v>
+        <v>1146428</v>
       </c>
       <c r="B41" t="n">
-        <v>159413</v>
+        <v>169010</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>豐盛燒味</t>
+          <t>味千拉麵</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1768,105 +1768,6 @@
         </is>
       </c>
       <c r="G41" t="inlineStr">
-        <is>
-          <t>2/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1139328</v>
-      </c>
-      <c r="B42" t="n">
-        <v>163860</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>鰹烏冬</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1/0</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2/29</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>1139855</v>
-      </c>
-      <c r="B43" t="n">
-        <v>165669</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>大勝豬扒·清湯腩</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1/0</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>3/0</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>1146428</v>
-      </c>
-      <c r="B44" t="n">
-        <v>169010</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>味千拉麵</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1/0</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
         <is>
           <t>5/8</t>
         </is>
